--- a/Demo-DataDrivenTesting/src/test/resources/InputFile.xlsx
+++ b/Demo-DataDrivenTesting/src/test/resources/InputFile.xlsx
@@ -4,19 +4,20 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="400" yWindow="320" windowWidth="18780" windowHeight="7020" activeTab="1"/>
+    <workbookView xWindow="400" yWindow="320" windowWidth="18780" windowHeight="7020" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="10">
   <si>
     <t>Email</t>
   </si>
@@ -34,6 +35,18 @@
   </si>
   <si>
     <t>dfbe</t>
+  </si>
+  <si>
+    <t>KeyWords</t>
+  </si>
+  <si>
+    <t>mac</t>
+  </si>
+  <si>
+    <t>Keyword</t>
+  </si>
+  <si>
+    <t>Selenium</t>
   </si>
 </sst>
 </file>
@@ -445,9 +458,41 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
+  <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>